--- a/data/trans_camb/P19C05-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P19C05-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 6,48</t>
+          <t>-2,11; 7,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,63; -0,32</t>
+          <t>-8,69; -0,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,28; -0,72</t>
+          <t>-8,64; -0,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 6,49</t>
+          <t>-2,48; 6,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,44; -2,05</t>
+          <t>-10,25; -1,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,45; -0,15</t>
+          <t>-7,53; -0,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 5,52</t>
+          <t>-1,22; 5,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,02; -2,18</t>
+          <t>-8,29; -2,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,0; -1,56</t>
+          <t>-6,61; -1,53</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-14,79; 51,36</t>
+          <t>-12,51; 56,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-49,79; -0,9</t>
+          <t>-50,47; -3,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-47,11; -4,38</t>
+          <t>-49,39; -5,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,96; 41,47</t>
+          <t>-12,95; 43,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-51,73; -13,6</t>
+          <t>-51,29; -9,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-36,82; -1,68</t>
+          <t>-36,48; -1,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 36,6</t>
+          <t>-6,99; 36,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-44,66; -14,06</t>
+          <t>-45,83; -13,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-38,02; -10,48</t>
+          <t>-36,69; -10,08</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 3,89</t>
+          <t>-3,28; 4,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 1,56</t>
+          <t>-5,36; 1,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,0; -2,41</t>
+          <t>-10,98; -2,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 6,53</t>
+          <t>-0,69; 6,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,82; -0,16</t>
+          <t>-6,99; 0,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,07; -3,24</t>
+          <t>-9,2; -3,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 4,45</t>
+          <t>-0,88; 4,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,08; -0,2</t>
+          <t>-5,25; -0,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-9,24; -3,97</t>
+          <t>-9,62; -4,06</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-20,15; 31,65</t>
+          <t>-20,76; 34,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-34,91; 13,79</t>
+          <t>-34,56; 13,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-71,72; -19,87</t>
+          <t>-71,06; -21,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 47,77</t>
+          <t>-3,82; 48,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-40,7; 0,16</t>
+          <t>-40,53; 0,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-52,3; -24,7</t>
+          <t>-52,89; -25,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 34,15</t>
+          <t>-5,98; 32,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-31,75; -0,91</t>
+          <t>-32,66; -1,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-61,31; -30,58</t>
+          <t>-62,92; -30,42</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 3,33</t>
+          <t>-5,55; 3,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,19; -2,52</t>
+          <t>-10,47; -2,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,73; -0,83</t>
+          <t>-8,83; -1,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 5,25</t>
+          <t>-3,72; 5,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,31; -2,12</t>
+          <t>-10,14; -1,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,68; -3,28</t>
+          <t>-14,51; -3,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 2,87</t>
+          <t>-3,12; 2,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,31; -3,79</t>
+          <t>-9,11; -3,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-10,34; -3,54</t>
+          <t>-10,42; -3,46</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-32,36; 28,48</t>
+          <t>-32,8; 26,9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-62,3; -19,61</t>
+          <t>-62,0; -20,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-50,69; -6,76</t>
+          <t>-51,65; -9,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-19,37; 36,83</t>
+          <t>-19,84; 35,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-54,2; -14,21</t>
+          <t>-54,1; -13,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-75,0; -22,02</t>
+          <t>-74,78; -21,09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-19,76; 20,17</t>
+          <t>-17,96; 20,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-55,13; -25,88</t>
+          <t>-53,09; -24,85</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-64,4; -24,98</t>
+          <t>-61,19; -24,45</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,69; 7,58</t>
+          <t>0,85; 7,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 2,91</t>
+          <t>-3,81; 2,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 2,3</t>
+          <t>-3,64; 2,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 5,44</t>
+          <t>-1,25; 5,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,21; -0,18</t>
+          <t>-6,92; -0,08</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 0,51</t>
+          <t>-6,34; 0,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,63; 5,53</t>
+          <t>0,6; 5,5</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 0,36</t>
+          <t>-4,62; 0,31</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 0,69</t>
+          <t>-4,16; 0,53</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,73; 72,12</t>
+          <t>4,99; 71,89</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-26,3; 29,1</t>
+          <t>-28,07; 28,21</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-25,51; 22,31</t>
+          <t>-26,6; 22,38</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-11,75; 39,15</t>
+          <t>-7,86; 43,28</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-40,86; -1,25</t>
+          <t>-39,1; -0,6</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-37,43; 2,85</t>
+          <t>-36,33; 2,79</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,02; 42,89</t>
+          <t>3,83; 43,66</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-28,95; 3,37</t>
+          <t>-30,46; 2,38</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-26,51; 5,3</t>
+          <t>-27,39; 3,97</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 3,33</t>
+          <t>-0,56; 3,1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,86; -1,13</t>
+          <t>-4,66; -1,24</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,43; -2,15</t>
+          <t>-6,82; -2,38</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,14; 3,98</t>
+          <t>0,12; 4,18</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,21; -2,58</t>
+          <t>-6,38; -2,67</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,53; -3,12</t>
+          <t>-7,37; -3,15</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,25</t>
+          <t>0,34; 3,1</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,02; -2,46</t>
+          <t>-5,13; -2,42</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,34; -3,25</t>
+          <t>-6,17; -3,27</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 26,18</t>
+          <t>-3,9; 24,38</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-33,01; -8,87</t>
+          <t>-32,58; -9,71</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-45,19; -17,27</t>
+          <t>-46,88; -18,62</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>0,86; 26,31</t>
+          <t>0,72; 27,54</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-36,72; -16,71</t>
+          <t>-37,63; -17,64</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-45,19; -20,92</t>
+          <t>-44,52; -21,06</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,8; 22,8</t>
+          <t>2,17; 21,78</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-32,03; -16,88</t>
+          <t>-32,71; -16,9</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-40,98; -22,72</t>
+          <t>-40,68; -22,82</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C05-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P19C05-Habitat-trans_camb.xlsx
@@ -634,37 +634,37 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>-4,64</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2,03</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>-5,95</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>-4,06</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,07</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>-5,27</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>-4,38</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,03</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-5,95</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-3,71</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,07</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-5,27</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>-4,08</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 7,14</t>
+          <t>-2,28; 6,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,69; -0,46</t>
+          <t>-8,43; -0,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,64; -0,95</t>
+          <t>-8,32; -1,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 6,81</t>
+          <t>-3,14; 6,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,25; -1,53</t>
+          <t>-10,06; -1,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,53; -0,21</t>
+          <t>-7,81; -0,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 5,42</t>
+          <t>-0,94; 5,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,29; -2,0</t>
+          <t>-8,18; -2,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,61; -1,53</t>
+          <t>-7,05; -1,85</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-29,63%</t>
+          <t>-31,37%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-20,89%</t>
+          <t>-22,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-24,91%</t>
+          <t>-26,74%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,51; 56,29</t>
+          <t>-14,28; 54,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-50,47; -3,58</t>
+          <t>-50,87; -4,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-49,39; -5,31</t>
+          <t>-48,68; -8,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,95; 43,06</t>
+          <t>-15,49; 40,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-51,29; -9,37</t>
+          <t>-50,5; -10,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-36,48; -1,69</t>
+          <t>-38,23; -5,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 36,22</t>
+          <t>-5,47; 36,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-45,83; -13,0</t>
+          <t>-45,65; -15,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-36,69; -10,08</t>
+          <t>-38,73; -12,79</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-6,11</t>
+          <t>-4,35</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-6,24</t>
+          <t>-6,28</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-6,31</t>
+          <t>-5,36</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 4,13</t>
+          <t>-3,32; 3,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 1,61</t>
+          <t>-5,36; 1,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,98; -2,51</t>
+          <t>-7,48; -1,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 6,68</t>
+          <t>-0,3; 6,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 0,06</t>
+          <t>-7,22; 0,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,2; -3,28</t>
+          <t>-9,33; -3,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 4,37</t>
+          <t>-0,62; 4,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,25; -0,14</t>
+          <t>-5,17; -0,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-9,62; -4,06</t>
+          <t>-7,89; -3,36</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-44,84%</t>
+          <t>-31,93%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-40,61%</t>
+          <t>-40,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-43,37%</t>
+          <t>-36,88%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-20,76; 34,98</t>
+          <t>-21,16; 36,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-34,56; 13,37</t>
+          <t>-34,43; 17,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-71,06; -21,37</t>
+          <t>-48,28; -11,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 48,85</t>
+          <t>-1,69; 52,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-40,53; 0,92</t>
+          <t>-40,4; 0,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-52,89; -25,62</t>
+          <t>-53,49; -25,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 32,49</t>
+          <t>-3,97; 33,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-32,66; -1,1</t>
+          <t>-32,71; -3,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-62,92; -30,42</t>
+          <t>-48,59; -25,74</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-4,93</t>
+          <t>-4,22</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-7,49</t>
+          <t>-4,32</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-6,29</t>
+          <t>-4,29</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 3,2</t>
+          <t>-5,68; 3,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,47; -2,58</t>
+          <t>-10,79; -2,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,83; -1,25</t>
+          <t>-8,12; -0,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 5,14</t>
+          <t>-3,37; 5,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,14; -1,95</t>
+          <t>-10,23; -2,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-14,51; -3,2</t>
+          <t>-7,68; -0,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 2,9</t>
+          <t>-3,46; 2,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,11; -3,56</t>
+          <t>-9,18; -3,5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-10,42; -3,46</t>
+          <t>-6,8; -1,32</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-33,65%</t>
+          <t>-28,83%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-44,99%</t>
+          <t>-25,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-40,08%</t>
+          <t>-27,35%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-32,8; 26,9</t>
+          <t>-33,63; 24,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-62,0; -20,37</t>
+          <t>-63,13; -20,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-51,65; -9,84</t>
+          <t>-48,6; -3,3</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-19,84; 35,11</t>
+          <t>-18,51; 35,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-54,1; -13,31</t>
+          <t>-54,88; -15,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-74,78; -21,09</t>
+          <t>-40,42; -4,38</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-17,96; 20,3</t>
+          <t>-20,63; 19,64</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-53,09; -24,85</t>
+          <t>-53,78; -24,72</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-61,19; -24,45</t>
+          <t>-39,43; -9,9</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,41</t>
+          <t>-0,29</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,66</t>
+          <t>-1,75</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-1,6</t>
+          <t>-1,07</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,85; 7,51</t>
+          <t>0,52; 7,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 2,83</t>
+          <t>-3,66; 2,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 2,36</t>
+          <t>-3,54; 2,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 5,92</t>
+          <t>-1,38; 5,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,92; -0,08</t>
+          <t>-6,79; 0,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 0,42</t>
+          <t>-5,11; 1,11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,5</t>
+          <t>0,64; 5,82</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 0,31</t>
+          <t>-4,41; 0,31</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 0,53</t>
+          <t>-3,28; 0,95</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-3,45%</t>
+          <t>-2,41%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-17,2%</t>
+          <t>-11,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-11,57%</t>
+          <t>-7,77%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,99; 71,89</t>
+          <t>3,95; 73,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-28,07; 28,21</t>
+          <t>-26,86; 27,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-26,6; 22,38</t>
+          <t>-25,52; 27,43</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 43,28</t>
+          <t>-8,25; 40,77</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-39,1; -0,6</t>
+          <t>-39,87; 0,45</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-36,33; 2,79</t>
+          <t>-28,62; 8,27</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,83; 43,66</t>
+          <t>4,05; 45,98</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-30,46; 2,38</t>
+          <t>-29,49; 2,33</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-27,39; 3,97</t>
+          <t>-21,41; 7,92</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-4,03</t>
+          <t>-3,22</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-5,01</t>
+          <t>-4,07</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-4,57</t>
+          <t>-3,69</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 3,1</t>
+          <t>-0,31; 3,38</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,66; -1,24</t>
+          <t>-4,65; -1,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,82; -2,38</t>
+          <t>-5,04; -1,39</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,12; 4,18</t>
+          <t>-0,07; 3,99</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,38; -2,67</t>
+          <t>-6,26; -2,52</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,37; -3,15</t>
+          <t>-5,67; -2,41</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,1</t>
+          <t>0,34; 3,19</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,13; -2,42</t>
+          <t>-5,15; -2,37</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,17; -3,27</t>
+          <t>-4,86; -2,36</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-29,68%</t>
+          <t>-23,71%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-31,08%</t>
+          <t>-25,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-30,6%</t>
+          <t>-24,69%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 24,38</t>
+          <t>-2,47; 26,24</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-32,58; -9,71</t>
+          <t>-32,01; -8,31</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-46,88; -18,62</t>
+          <t>-33,48; -10,89</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>0,72; 27,54</t>
+          <t>-0,54; 26,34</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-37,63; -17,64</t>
+          <t>-37,33; -17,17</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-44,52; -21,06</t>
+          <t>-33,01; -16,23</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,17; 21,78</t>
+          <t>2,06; 22,1</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-32,71; -16,9</t>
+          <t>-32,3; -16,15</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-40,68; -22,82</t>
+          <t>-31,14; -17,03</t>
         </is>
       </c>
     </row>
